--- a/artfynd/A 57391-2025 artfynd.xlsx
+++ b/artfynd/A 57391-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131424979</v>
       </c>
       <c r="B2" t="n">
-        <v>92276</v>
+        <v>92277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131426717</v>
       </c>
       <c r="B3" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131426845</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131425315</v>
       </c>
       <c r="B5" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131425680</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57391-2025 artfynd.xlsx
+++ b/artfynd/A 57391-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131424979</v>
       </c>
       <c r="B2" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131426717</v>
       </c>
       <c r="B3" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131426845</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131425315</v>
       </c>
       <c r="B5" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131425680</v>
       </c>
       <c r="B6" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57391-2025 artfynd.xlsx
+++ b/artfynd/A 57391-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131424979</v>
       </c>
       <c r="B2" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131426717</v>
       </c>
       <c r="B3" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131426845</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131425315</v>
       </c>
       <c r="B5" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131425680</v>
       </c>
       <c r="B6" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57391-2025 artfynd.xlsx
+++ b/artfynd/A 57391-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131424979</v>
+        <v>131425680</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>131426717</v>
       </c>
       <c r="B3" t="n">
-        <v>92599</v>
+        <v>92662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131426845</v>
+        <v>131425315</v>
       </c>
       <c r="B4" t="n">
-        <v>58071</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609912</v>
+        <v>609876</v>
       </c>
       <c r="R4" t="n">
-        <v>6922923</v>
+        <v>6922986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131425315</v>
+        <v>131424979</v>
       </c>
       <c r="B5" t="n">
-        <v>91846</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131425680</v>
+        <v>131426146</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609876</v>
+        <v>609861</v>
       </c>
       <c r="R6" t="n">
-        <v>6922986</v>
+        <v>6923069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131426845</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännorna, Brännorna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609912</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6922923</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57391-2025 artfynd.xlsx
+++ b/artfynd/A 57391-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131425680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131426717</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131425315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131424979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131426146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131426845</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>